--- a/output/full_scan/batch_seq0_2026-07-22.xlsx
+++ b/output/full_scan/batch_seq0_2026-07-22.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O114"/>
+  <dimension ref="A1:O117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -845,21 +845,21 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>8462</v>
+        <v>8383</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>627.2401348707583</v>
+        <v>653.3889746458735</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>156</v>
+        <v>83.7</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>57.99244236895751</v>
+        <v>63.6575830008567</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>35.93634854746055</v>
+        <v>37.63241045452315</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.4654252514382894</v>
+        <v>0.4562133132282052</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.0532098577652675</v>
+        <v>1.353008725256402</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8093</v>
+        <v>8462</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>621.8470481919686</v>
+        <v>627.2401348707583</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>20.75</v>
+        <v>156</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>56.14730397918363</v>
+        <v>57.99244236895751</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>11.04608326108368</v>
+        <v>35.93634854746055</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.148397156735138</v>
+        <v>0.4654252514382894</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-0.0149796894249714</v>
+        <v>0.0532098577652675</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8464</v>
+        <v>8093</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>607.7687842161266</v>
+        <v>621.8470481919686</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>363</v>
+        <v>20.75</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>55.52958160595971</v>
+        <v>56.14730397918363</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>25.2864001494763</v>
+        <v>11.04608326108368</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.5451501440426719</v>
+        <v>1.148397156735138</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-1.022815370184636</v>
+        <v>-0.0149796894249714</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8109</v>
+        <v>8464</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>博大</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>590.0008667654413</v>
+        <v>607.7687842161266</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>130.5</v>
+        <v>363</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>48.55019502945557</v>
+        <v>55.52958160595971</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>23.75426658570541</v>
+        <v>25.2864001494763</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.6518754873652188</v>
+        <v>0.5451501440426719</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-1.974641421932868</v>
+        <v>-1.022815370184636</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>8147</v>
+        <v>8109</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>博大</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>586.4493617156131</v>
+        <v>590.0008667654413</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>131</v>
+        <v>130.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>35.32826989520521</v>
+        <v>48.55019502945557</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>21.38884525766456</v>
+        <v>23.75426658570541</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.8593599602473877</v>
+        <v>0.6518754873652188</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-1.487831260740486</v>
+        <v>-1.974641421932868</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8476</v>
+        <v>8147</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>541.025671355019</v>
+        <v>586.4493617156131</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>23.25</v>
+        <v>131</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>55.34904217205035</v>
+        <v>35.32826989520521</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>37.21403883102312</v>
+        <v>21.38884525766456</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.5274553825468227</v>
+        <v>0.8593599602473877</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-0.2281395526576255</v>
+        <v>-1.487831260740486</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8150</v>
+        <v>8476</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>535.7678109958085</v>
+        <v>541.025671355019</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>100</v>
+        <v>23.25</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>47.24422347260414</v>
+        <v>55.34904217205035</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>23.38915564277451</v>
+        <v>37.21403883102312</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.396551587214408</v>
+        <v>0.5274553825468227</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-1.589297177850925</v>
+        <v>-0.2281395526576255</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>8102</v>
+        <v>8150</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>504.1930283672818</v>
+        <v>535.7678109958085</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>58.64798534995108</v>
+        <v>47.24422347260414</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>15.71174187399603</v>
+        <v>23.38915564277451</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.9720264034862856</v>
+        <v>1.396551587214408</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.4429980879808427</v>
+        <v>-1.589297177850925</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8182</v>
+        <v>8102</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>500.5293512727491</v>
+        <v>504.1930283672818</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>41</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>39.86994547582882</v>
+        <v>58.64798534995108</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>20.23023537761189</v>
+        <v>15.71174187399603</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.1577806257223969</v>
+        <v>0.9720264034862856</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-1.624538983664017</v>
+        <v>0.4429980879808427</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8155</v>
+        <v>8182</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>500.4096654020613</v>
+        <v>500.5293512727491</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>309</v>
+        <v>41</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>37.07878116520042</v>
+        <v>39.86994547582882</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>26.43613910098464</v>
+        <v>20.23023537761189</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2.074998454454993</v>
+        <v>0.1577806257223969</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-5.855571804914362</v>
+        <v>-1.624538983664017</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8112</v>
+        <v>8155</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>495.5554504892324</v>
+        <v>500.4096654020613</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>88.09999999999999</v>
+        <v>309</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>49.49102683766856</v>
+        <v>37.07878116520042</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>13.1689586043066</v>
+        <v>26.43613910098464</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.929318807700028</v>
+        <v>2.074998454454993</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.3721913438255844</v>
+        <v>-5.855571804914362</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8111</v>
+        <v>8096</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>483.1559714316326</v>
+        <v>496.0843893485161</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>51.7</v>
+        <v>140.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>48.67418884971652</v>
+        <v>47.83446130081199</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>26.15164395744385</v>
+        <v>25.49380711255089</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.786511839696569</v>
+        <v>0.1245733456582532</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.2416180676235395</v>
+        <v>-3.917894277045446</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8932</v>
+        <v>8112</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>476.1270095115638</v>
+        <v>495.5554504892324</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>118</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>56.02863710880609</v>
+        <v>49.49102683766856</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>26.7487378965904</v>
+        <v>13.1689586043066</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.5117644570152797</v>
+        <v>1.929318807700028</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.0990138852595778</v>
+        <v>-0.3721913438255844</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8466</v>
+        <v>8111</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>474.6431351014909</v>
+        <v>483.1559714316326</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>17.5</v>
+        <v>51.7</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>58.1328770690065</v>
+        <v>48.67418884971652</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>24.91777406825963</v>
+        <v>26.15164395744385</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.7739515285542689</v>
+        <v>1.786511839696569</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.0129715869718228</v>
+        <v>0.2416180676235395</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8438</v>
+        <v>8932</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>470.5112307169542</v>
+        <v>476.1270095115638</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>70.2</v>
+        <v>118</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>29.20021904489202</v>
+        <v>56.02863710880609</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>26.88100412745353</v>
+        <v>26.7487378965904</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.2962648325680294</v>
+        <v>0.5117644570152797</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-3.407061202540016</v>
+        <v>-0.0990138852595778</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>9912</v>
+        <v>8466</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>465.2058900946849</v>
+        <v>474.6431351014909</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>12.45</v>
+        <v>17.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>41.8566170933525</v>
+        <v>58.1328770690065</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>17.18293352340495</v>
+        <v>24.91777406825963</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.4089775461613185</v>
+        <v>0.7739515285542689</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.0179500115756494</v>
+        <v>-0.0129715869718228</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8289</v>
+        <v>8438</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>463.5208088881694</v>
+        <v>470.5112307169542</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>45.25</v>
+        <v>70.2</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>28.02913408094895</v>
+        <v>29.20021904489202</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>25.41111342502557</v>
+        <v>26.88100412745353</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.274975922588169</v>
+        <v>0.2962648325680294</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-1.664718129602578</v>
+        <v>-3.407061202540016</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8071</v>
+        <v>9912</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>459.5821942725521</v>
+        <v>465.2058900946849</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>24.75</v>
+        <v>12.45</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>42.4400648376595</v>
+        <v>41.8566170933525</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>29.79828321286763</v>
+        <v>17.18293352340495</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.2223010370569985</v>
+        <v>0.4089775461613185</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-1.068087727299002</v>
+        <v>-0.0179500115756494</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8271</v>
+        <v>8289</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>451.9204888432238</v>
+        <v>463.5208088881694</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>196.5</v>
+        <v>45.25</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>51.0059725639985</v>
+        <v>28.02913408094895</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>22.1986998726311</v>
+        <v>25.41111342502557</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.315610717558142</v>
+        <v>0.274975922588169</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>2.052628009529319</v>
+        <v>-1.664718129602578</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8234</v>
+        <v>8071</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>445.9676016223872</v>
+        <v>459.5821942725521</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>63.9</v>
+        <v>24.75</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>45.33269681279381</v>
+        <v>42.4400648376595</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>21.69936388602144</v>
+        <v>29.79828321286763</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.4250708450965023</v>
+        <v>0.2223010370569985</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.9823046506508636</v>
+        <v>-1.068087727299002</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8222</v>
+        <v>8271</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>443.6350312524799</v>
+        <v>451.9204888432238</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>39.9</v>
+        <v>196.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>52.35289896763513</v>
+        <v>51.0059725639985</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>26.77135207082165</v>
+        <v>22.1986998726311</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.763503125247987</v>
+        <v>1.315610717558142</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.2380313167961893</v>
+        <v>2.052628009529319</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>9905</v>
+        <v>8234</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>大華</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>439.2585379873698</v>
+        <v>445.9676016223872</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>20.6</v>
+        <v>63.9</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>41.46795168821308</v>
+        <v>45.33269681279381</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>24.58043379089404</v>
+        <v>21.69936388602144</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.6869003632162353</v>
+        <v>0.4250708450965023</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.0519240623386298</v>
+        <v>-0.9823046506508636</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8074</v>
+        <v>8222</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>432.1601992583965</v>
+        <v>443.6350312524799</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>57</v>
+        <v>39.9</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>36.19416411166342</v>
+        <v>52.35289896763513</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>29.60867631080128</v>
+        <v>26.77135207082165</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.812300654502826</v>
+        <v>1.763503125247987</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.7228550809817333</v>
+        <v>-0.2380313167961893</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8068</v>
+        <v>9905</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>大華</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>430.144825770438</v>
+        <v>439.2585379873698</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>19.1</v>
+        <v>20.6</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>49.95037790375938</v>
+        <v>41.46795168821308</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>13.21387382389643</v>
+        <v>24.58043379089404</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.7813967841284604</v>
+        <v>0.6869003632162353</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.0895893463017253</v>
+        <v>-0.0519240623386298</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8080</v>
+        <v>8074</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>429.4731647593749</v>
+        <v>432.1601992583965</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>28.55</v>
+        <v>57</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>59.92265858659445</v>
+        <v>36.19416411166342</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>39.82022629532311</v>
+        <v>29.60867631080128</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.7757042488513877</v>
+        <v>1.812300654502826</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.0305919677985574</v>
+        <v>-0.7228550809817333</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, cci_momentum</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8996</v>
+        <v>8068</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>419.1294335594121</v>
+        <v>430.144825770438</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>1080</v>
+        <v>19.1</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>40.59614198150957</v>
+        <v>49.95037790375938</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>25.26855123364932</v>
+        <v>13.21387382389643</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.537962653196167</v>
+        <v>0.7813967841284604</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-45.04874884559322</v>
+        <v>0.0895893463017253</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8404</v>
+        <v>8080</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>410.1354324402543</v>
+        <v>429.4731647593749</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>16.95</v>
+        <v>28.55</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>51.89803803169873</v>
+        <v>59.92265858659445</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>23.37409674149377</v>
+        <v>39.82022629532311</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.7560361942761867</v>
+        <v>0.7757042488513877</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.0433933557720477</v>
+        <v>0.0305919677985574</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8131</v>
+        <v>8996</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>405.6029610371533</v>
+        <v>419.1294335594121</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>71.8</v>
+        <v>1080</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>48.68432802363333</v>
+        <v>40.59614198150957</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>13.27525384335645</v>
+        <v>25.26855123364932</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.7615143622634638</v>
+        <v>1.537962653196167</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-1.025556627182609</v>
+        <v>-45.04874884559322</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8121</v>
+        <v>8404</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>394.2515591666447</v>
+        <v>410.1354324402543</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>34.5</v>
+        <v>16.95</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>33.06802736180003</v>
+        <v>51.89803803169873</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>26.64227863702787</v>
+        <v>23.37409674149377</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.473436318930958</v>
+        <v>0.7560361942761867</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-1.608512303481382</v>
+        <v>0.0433933557720477</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8499</v>
+        <v>8131</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>390.343125869149</v>
+        <v>405.6029610371533</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>269.5</v>
+        <v>71.8</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>40.16463950455269</v>
+        <v>48.68432802363333</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>14.04281674213134</v>
+        <v>13.27525384335645</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.5343287889849069</v>
+        <v>0.7615143622634638</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-4.386756673123083</v>
+        <v>-1.025556627182609</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8240</v>
+        <v>8121</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>386.7327245141623</v>
+        <v>394.2515591666447</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>42.7</v>
+        <v>34.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>27.27929859929151</v>
+        <v>33.06802736180003</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>30.32818609077696</v>
+        <v>26.64227863702787</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.6934949595951778</v>
+        <v>0.473436318930958</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.4578856465759249</v>
+        <v>-1.608512303481382</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8183</v>
+        <v>8499</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>384.696384352737</v>
+        <v>390.343125869149</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>31.25</v>
+        <v>269.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>43.67461936950178</v>
+        <v>40.16463950455269</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>23.10854593421723</v>
+        <v>14.04281674213134</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.2830443645048797</v>
+        <v>0.5343287889849069</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.40959069983903</v>
+        <v>-4.386756673123083</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8442</v>
+        <v>8240</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>381.2587134547876</v>
+        <v>386.7327245141623</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>45.1</v>
+        <v>42.7</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>58.21240733479339</v>
+        <v>27.27929859929151</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>40.6388162230118</v>
+        <v>30.32818609077696</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.3053250526049575</v>
+        <v>0.6934949595951778</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.1969893509896165</v>
+        <v>-0.4578856465759249</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8926</v>
+        <v>8291</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>379.5309736602661</v>
+        <v>386.5015814229014</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>64.7</v>
+        <v>39.95</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>38.07536549726515</v>
+        <v>50.02126357334861</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>29.11119973517264</v>
+        <v>28.88322145790591</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.5131573371203549</v>
+        <v>0.5106283653807457</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-1.677183162788905</v>
+        <v>1.418162430390017</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8103</v>
+        <v>8183</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>368.1915784939952</v>
+        <v>384.696384352737</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>80</v>
+        <v>31.25</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>34.48484963155833</v>
+        <v>43.67461936950178</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>29.04393726592778</v>
+        <v>23.10854593421723</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.4555188835524444</v>
+        <v>0.2830443645048797</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-1.646465138801901</v>
+        <v>-0.40959069983903</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8210</v>
+        <v>8442</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>365.4176396615845</v>
+        <v>381.2587134547876</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>1150</v>
+        <v>45.1</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>42.740384424978</v>
+        <v>58.21240733479339</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>25.0920310031091</v>
+        <v>40.6388162230118</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.428334333837698</v>
+        <v>0.3053250526049575</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-4.704079166241662</v>
+        <v>0.1969893509896165</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8390</v>
+        <v>8926</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>364.7407223112977</v>
+        <v>379.5309736602661</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>96.2</v>
+        <v>64.7</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>37.34477994530239</v>
+        <v>38.07536549726515</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>27.29870021718146</v>
+        <v>29.11119973517264</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.5404041370851973</v>
+        <v>0.5131573371203549</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.8299180704622318</v>
+        <v>-1.677183162788905</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2806,21 +2806,21 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8104</v>
+        <v>8103</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>364.3742563903189</v>
+        <v>368.1915784939952</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>34.3</v>
+        <v>80</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>37.40896960737939</v>
+        <v>34.48484963155833</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>20.6839053692753</v>
+        <v>29.04393726592778</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.1917024408563437</v>
+        <v>0.4555188835524444</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.7280694678493667</v>
+        <v>-1.646465138801901</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8488</v>
+        <v>8210</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>361.9805970018174</v>
+        <v>365.4176396615845</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>10.1</v>
+        <v>1150</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>51.33339073583014</v>
+        <v>42.740384424978</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>11.6646188691795</v>
+        <v>25.0920310031091</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.1508244837239223</v>
+        <v>1.428334333837698</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.0568704569623439</v>
+        <v>-4.704079166241662</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8443</v>
+        <v>8390</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>356.9672173256314</v>
+        <v>364.7407223112977</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>11.35</v>
+        <v>96.2</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>43.61767423953858</v>
+        <v>37.34477994530239</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>48.26166151442713</v>
+        <v>27.29870021718146</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.1920441461214718</v>
+        <v>0.5404041370851973</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.0070302314799553</v>
+        <v>-0.8299180704622318</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8227</v>
+        <v>8104</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>353.9931009953024</v>
+        <v>364.3742563903189</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>154.5</v>
+        <v>34.3</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>38.44023598005595</v>
+        <v>37.40896960737939</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>21.81821275982252</v>
+        <v>20.6839053692753</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.2367620997954581</v>
+        <v>0.1917024408563437</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-4.461881574332146</v>
+        <v>-0.7280694678493667</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8081</v>
+        <v>8488</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>351.9258701589056</v>
+        <v>361.9805970018174</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>253</v>
+        <v>10.1</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>39.39137484338493</v>
+        <v>51.33339073583014</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>30.64590710395465</v>
+        <v>11.6646188691795</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.73969788583452</v>
+        <v>0.1508244837239223</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-6.878149523986854</v>
+        <v>0.0568704569623439</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8163</v>
+        <v>8443</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>351.905291390563</v>
+        <v>356.9672173256314</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>32.85</v>
+        <v>11.35</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>34.43600653873322</v>
+        <v>43.61767423953858</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>26.17843194569512</v>
+        <v>48.26166151442713</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.3880843803582327</v>
+        <v>0.1920441461214718</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.8875880867647163</v>
+        <v>-0.0070302314799553</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8086</v>
+        <v>8227</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>349.083206314983</v>
+        <v>353.9931009953024</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>122.5</v>
+        <v>154.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>36.77433906580065</v>
+        <v>38.44023598005595</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>24.87167659659967</v>
+        <v>21.81821275982252</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.6531466238945373</v>
+        <v>0.2367620997954581</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-1.795428250200659</v>
+        <v>-4.461881574332146</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3177,21 +3177,21 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8069</v>
+        <v>8081</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>338.6562365409959</v>
+        <v>351.9258701589056</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>194.5</v>
+        <v>253</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,49 +3202,49 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>48.79325971169801</v>
+        <v>39.39137484338493</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>14.3882159345825</v>
+        <v>30.64590710395465</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.499686381756502</v>
+        <v>0.73969788583452</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-1.140741275019144</v>
+        <v>-6.878149523986854</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8070</v>
+        <v>8163</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>337.4151577895849</v>
+        <v>351.905291390563</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>49</v>
+        <v>32.85</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>41.33196568465241</v>
+        <v>34.43600653873322</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>20.5705227035765</v>
+        <v>26.17843194569512</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.5156833855640727</v>
+        <v>0.3880843803582327</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.7990520459262452</v>
+        <v>-0.8875880867647163</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3283,21 +3283,21 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8088</v>
+        <v>8086</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>335.7453280418729</v>
+        <v>349.083206314983</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>48.65</v>
+        <v>122.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>35.89758077935888</v>
+        <v>36.77433906580065</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>25.1850097055049</v>
+        <v>24.87167659659967</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.6640872454388564</v>
+        <v>0.6531466238945373</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-1.238013453179033</v>
+        <v>-1.795428250200659</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8299</v>
+        <v>8069</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>335.2047125199217</v>
+        <v>338.6562365409959</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>1915</v>
+        <v>194.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,49 +3361,49 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>39.77157927150056</v>
+        <v>48.79325971169801</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>20.15381279302055</v>
+        <v>14.3882159345825</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.9054702021261962</v>
+        <v>1.499686381756502</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M55" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-37.53305918078003</v>
+        <v>-1.140741275019144</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8171</v>
+        <v>8070</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>331.9837449488448</v>
+        <v>337.4151577895849</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>20.9</v>
+        <v>49</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>46.63774546088175</v>
+        <v>41.33196568465241</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>14.45744686562531</v>
+        <v>20.5705227035765</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.9573897009693484</v>
+        <v>0.5156833855640727</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.1009794065520348</v>
+        <v>-0.7990520459262452</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>9908</v>
+        <v>8088</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>大台北</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>328.6063708490996</v>
+        <v>335.7453280418729</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>29</v>
+        <v>48.65</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>37.25923183934287</v>
+        <v>35.89758077935888</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>22.47774928871643</v>
+        <v>25.1850097055049</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.309595903395862</v>
+        <v>0.6640872454388564</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.0879614330698109</v>
+        <v>-1.238013453179033</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8374</v>
+        <v>8299</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>321.1780843065777</v>
+        <v>335.2047125199217</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>79</v>
+        <v>1915</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,49 +3520,49 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>38.98033173318205</v>
+        <v>39.77157927150056</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>14.68793244922506</v>
+        <v>20.15381279302055</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.3501667558434821</v>
+        <v>0.9054702021261962</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.7240221067349464</v>
+        <v>-37.53305918078003</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8105</v>
+        <v>8171</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>309.3360593447121</v>
+        <v>331.9837449488448</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>17.8</v>
+        <v>20.9</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>41.83515041848177</v>
+        <v>46.63774546088175</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>29.3256241997076</v>
+        <v>14.45744686562531</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.6002153604951852</v>
+        <v>0.9573897009693484</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.5264087294611033</v>
+        <v>0.1009794065520348</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>8054</v>
+        <v>9908</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>大台北</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>302.7961058454394</v>
+        <v>328.6063708490996</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>96.5</v>
+        <v>29</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>43.31845019684092</v>
+        <v>37.25923183934287</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>20.40468711245546</v>
+        <v>22.47774928871643</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6934892142674273</v>
+        <v>1.309595903395862</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-1.463654356511645</v>
+        <v>-0.0879614330698109</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>9930</v>
+        <v>8374</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>302.7521529394804</v>
+        <v>321.1780843065777</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>62.8</v>
+        <v>79</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>31.81784055365098</v>
+        <v>38.98033173318205</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>49.74175378758458</v>
+        <v>14.68793244922506</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.852730280886717</v>
+        <v>0.3501667558434821</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.0250552047166272</v>
+        <v>-0.7240221067349464</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8455</v>
+        <v>8105</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>297.9210713177007</v>
+        <v>309.3360593447121</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>26.3</v>
+        <v>17.8</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>44.27802658162715</v>
+        <v>41.83515041848177</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>19.40635840922951</v>
+        <v>29.3256241997076</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.432568419072698</v>
+        <v>0.6002153604951852</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.07342797080425729</v>
+        <v>-0.5264087294611033</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8215</v>
+        <v>8054</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>297.0815818499043</v>
+        <v>302.7961058454394</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>25.1</v>
+        <v>96.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>37.89622697558617</v>
+        <v>43.31845019684092</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>21.68007226565104</v>
+        <v>20.40468711245546</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.267975972087335</v>
+        <v>0.6934892142674273</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.465145542007675</v>
+        <v>-1.463654356511645</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8478</v>
+        <v>9930</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>295.2678002721723</v>
+        <v>302.7521529394804</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>152</v>
+        <v>62.8</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>45.6692893358896</v>
+        <v>31.81784055365098</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>13.33765853002896</v>
+        <v>49.74175378758458</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.6327329325648805</v>
+        <v>1.852730280886717</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.3100864373820977</v>
+        <v>0.0250552047166272</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>9136</v>
+        <v>8455</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>287.3051431870353</v>
+        <v>297.9210713177007</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>11.1</v>
+        <v>26.3</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>33.10061237750911</v>
+        <v>44.27802658162715</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>22.86812095140788</v>
+        <v>19.40635840922951</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.053383305512386</v>
+        <v>1.432568419072698</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.3754638132415561</v>
+        <v>0.07342797080425729</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8358</v>
+        <v>8215</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>283.0833747619078</v>
+        <v>297.0815818499043</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>412.5</v>
+        <v>25.1</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>36.03223784549356</v>
+        <v>37.89622697558617</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>19.82530094251739</v>
+        <v>21.68007226565104</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.372171927337157</v>
+        <v>0.267975972087335</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-18.08854903579676</v>
+        <v>-0.465145542007675</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8473</v>
+        <v>8478</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>280.1025718607582</v>
+        <v>295.2678002721723</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>44.5</v>
+        <v>152</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>43.06399708882996</v>
+        <v>45.6692893358896</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>20.67395303854232</v>
+        <v>13.33765853002896</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.6407628343033391</v>
+        <v>0.6327329325648805</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.4282314648711819</v>
+        <v>-0.3100864373820977</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8422</v>
+        <v>9136</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>279.2562631708154</v>
+        <v>287.3051431870353</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>26</v>
+        <v>11.1</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>41.36914036111282</v>
+        <v>33.10061237750911</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>14.70513086421537</v>
+        <v>22.86812095140788</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.4579770783531759</v>
+        <v>1.053383305512386</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.1367792061418191</v>
+        <v>-0.3754638132415561</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8076</v>
+        <v>8358</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>273.9333136851167</v>
+        <v>283.0833747619078</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>24.15</v>
+        <v>412.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>45.41024807058893</v>
+        <v>36.03223784549356</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>13.84502835019627</v>
+        <v>19.82530094251739</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.8488571017414638</v>
+        <v>1.372171927337157</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.2124349755753355</v>
+        <v>-18.08854903579676</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>9907</v>
+        <v>8473</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>統一實</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>273.6930537101237</v>
+        <v>280.1025718607582</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>15.15</v>
+        <v>44.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>41.51546682029083</v>
+        <v>43.06399708882996</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>25.75251412870661</v>
+        <v>20.67395303854232</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.6060754625987317</v>
+        <v>0.6407628343033391</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0405103729740229</v>
+        <v>-0.4282314648711819</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8162</v>
+        <v>8422</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>272.6915694608477</v>
+        <v>279.2562631708154</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>64.5</v>
+        <v>26</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>40.63051411360027</v>
+        <v>41.36914036111282</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>28.68081749720503</v>
+        <v>14.70513086421537</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.3591844472626185</v>
+        <v>0.4579770783531759</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-2.281405125480783</v>
+        <v>-0.1367792061418191</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8064</v>
+        <v>8076</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>270.9226219354685</v>
+        <v>273.9333136851167</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>115.5</v>
+        <v>24.15</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,49 +4262,49 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>40.14196251538581</v>
+        <v>45.41024807058893</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>17.39192987850926</v>
+        <v>13.84502835019627</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.5794365685973687</v>
+        <v>0.8488571017414638</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-3.123549143839825</v>
+        <v>-0.2124349755753355</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8367</v>
+        <v>9907</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>統一實</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>270.7776159772197</v>
+        <v>273.6930537101237</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>40.35</v>
+        <v>15.15</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>47.12526281498016</v>
+        <v>41.51546682029083</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>30.24987173249162</v>
+        <v>25.75251412870661</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.6630982860046515</v>
+        <v>0.6060754625987317</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.0596234136899994</v>
+        <v>0.0405103729740229</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8085</v>
+        <v>8162</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>269.9145256868163</v>
+        <v>272.6915694608477</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>11.3</v>
+        <v>64.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>40.59812930800831</v>
+        <v>40.63051411360027</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>23.80227623109288</v>
+        <v>28.68081749720503</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.7903019531204467</v>
+        <v>0.3591844472626185</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.0395034278878322</v>
+        <v>-2.281405125480783</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8110</v>
+        <v>8064</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>264.8281278516321</v>
+        <v>270.9226219354685</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>44.35</v>
+        <v>115.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,25 +4421,25 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>38.08130931214366</v>
+        <v>40.14196251538581</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>19.90774394413971</v>
+        <v>17.39192987850926</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.4245801666124743</v>
+        <v>0.5794365685973687</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-1.099593601251875</v>
+        <v>-3.123549143839825</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4449,21 +4449,21 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>9105</v>
+        <v>8367</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>261.9456770304596</v>
+        <v>270.7776159772197</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>8.68</v>
+        <v>40.35</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>46.57448875104245</v>
+        <v>47.12526281498016</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>19.02018415564757</v>
+        <v>30.24987173249162</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.494521799934237</v>
+        <v>0.6630982860046515</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.09028281573604981</v>
+        <v>0.0596234136899994</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8097</v>
+        <v>8085</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>259.7277485327836</v>
+        <v>269.9145256868163</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>52.5</v>
+        <v>11.3</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>30.41143759482824</v>
+        <v>40.59812930800831</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>15.5417600179085</v>
+        <v>23.80227623109288</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.2890344250955908</v>
+        <v>0.7903019531204467</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.6455627340426828</v>
+        <v>-0.0395034278878322</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8089</v>
+        <v>8110</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>253.4501504389281</v>
+        <v>264.8281278516321</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>18.9</v>
+        <v>44.35</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>40.53454004271163</v>
+        <v>38.08130931214366</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>22.95307379765438</v>
+        <v>19.90774394413971</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.3257120096501663</v>
+        <v>0.4245801666124743</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.1471429439718642</v>
+        <v>-1.099593601251875</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8454</v>
+        <v>9105</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>251.6628753394085</v>
+        <v>261.9456770304596</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>248</v>
+        <v>8.68</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>37.45845558322096</v>
+        <v>46.57448875104245</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>19.27432274120952</v>
+        <v>19.02018415564757</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.4469739116746291</v>
+        <v>0.494521799934237</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-5.141563262256696</v>
+        <v>-0.09028281573604981</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4661,21 +4661,21 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8213</v>
+        <v>8097</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>246.6007996389828</v>
+        <v>259.7277485327836</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>32.25</v>
+        <v>52.5</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>36.94252146522462</v>
+        <v>30.41143759482824</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>26.6942718366791</v>
+        <v>15.5417600179085</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.038561544448777</v>
+        <v>0.2890344250955908</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.3053116372393234</v>
+        <v>-0.6455627340426828</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8482</v>
+        <v>8089</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>243.9043892408712</v>
+        <v>253.4501504389281</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>47.85</v>
+        <v>18.9</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>51.25624866086991</v>
+        <v>40.53454004271163</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>4.495748316470096</v>
+        <v>22.95307379765438</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.5704971475142624</v>
+        <v>0.3257120096501663</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.2688070058879428</v>
+        <v>-0.1471429439718642</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8481</v>
+        <v>8454</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>237.5669973411971</v>
+        <v>251.6628753394085</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>40.2</v>
+        <v>248</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>38.13620860754988</v>
+        <v>37.45845558322096</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>19.21545171416116</v>
+        <v>19.27432274120952</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.3595189128183013</v>
+        <v>0.4469739116746291</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.2945609455673641</v>
+        <v>-5.141563262256696</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>9802</v>
+        <v>8213</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>鈺齊-KY</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>235.7194753824458</v>
+        <v>246.6007996389828</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>73.90000000000001</v>
+        <v>32.25</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>46.20353855159963</v>
+        <v>36.94252146522462</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>9.959699247479652</v>
+        <v>26.6942718366791</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.7626436593486375</v>
+        <v>1.038561544448777</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.1716594259960837</v>
+        <v>-0.3053116372393234</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8059</v>
+        <v>8482</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>229.9385922132283</v>
+        <v>243.9043892408712</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>15.9</v>
+        <v>47.85</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>40.95494060237858</v>
+        <v>51.25624866086991</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>23.82777452201633</v>
+        <v>4.495748316470096</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.3121134288685139</v>
+        <v>0.5704971475142624</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.0234769404840182</v>
+        <v>0.2688070058879428</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>8176</v>
+        <v>8481</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>229.869211165896</v>
+        <v>237.5669973411971</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>10.05</v>
+        <v>40.2</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>46.1444313046432</v>
+        <v>38.13620860754988</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>15.63241023726749</v>
+        <v>19.21545171416116</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.3005068698151961</v>
+        <v>0.3595189128183013</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.0409495758879297</v>
+        <v>-0.2945609455673641</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>9911</v>
+        <v>9802</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>櫻花</t>
+          <t>鈺齊-KY</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>227.7700696362751</v>
+        <v>235.7194753824458</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>82.40000000000001</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>41.53765514314233</v>
+        <v>46.20353855159963</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>11.10810104356508</v>
+        <v>9.959699247479652</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.759818806391929</v>
+        <v>0.7626436593486375</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.1482954665537099</v>
+        <v>0.1716594259960837</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8049</v>
+        <v>8059</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>207.7797999651745</v>
+        <v>229.9385922132283</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>26.15</v>
+        <v>15.9</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>42.9464747688155</v>
+        <v>40.95494060237858</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>16.44454167413086</v>
+        <v>23.82777452201633</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.4331700291987039</v>
+        <v>0.3121134288685139</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.1184615976498406</v>
+        <v>0.0234769404840182</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8048</v>
+        <v>8176</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>206.2551421114016</v>
+        <v>229.869211165896</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>57</v>
+        <v>10.05</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>38.47954287329955</v>
+        <v>46.1444313046432</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>19.15754358296457</v>
+        <v>15.63241023726749</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.227399229893634</v>
+        <v>0.3005068698151961</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.5486786488848596</v>
+        <v>-0.0409495758879297</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>9904</v>
+        <v>9911</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>櫻花</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>197.0525602224025</v>
+        <v>227.7700696362751</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>24.25</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>36.24112964698921</v>
+        <v>41.53765514314233</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>18.49709512000497</v>
+        <v>11.10810104356508</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.7808013114656017</v>
+        <v>1.759818806391929</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0323553241354109</v>
+        <v>-0.1482954665537099</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8101</v>
+        <v>8049</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>191.8491065808963</v>
+        <v>207.7797999651745</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>13.9</v>
+        <v>26.15</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>54.01575225329805</v>
+        <v>42.9464747688155</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>12.01319565585825</v>
+        <v>16.44454167413086</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.1321942307341771</v>
+        <v>0.4331700291987039</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0802758112579878</v>
+        <v>-0.1184615976498406</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8477</v>
+        <v>8048</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>191.107833446731</v>
+        <v>206.2551421114016</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>15.7</v>
+        <v>57</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>43.66880654878231</v>
+        <v>38.47954287329955</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>11.59743450407498</v>
+        <v>19.15754358296457</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.3549141663447051</v>
+        <v>1.227399229893634</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.0368426388481518</v>
+        <v>-0.5486786488848596</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5297,21 +5297,21 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8201</v>
+        <v>9904</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>187.9277744709509</v>
+        <v>197.0525602224025</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>12.1</v>
+        <v>24.25</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>37.47903948525873</v>
+        <v>36.24112964698921</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>13.44677456487144</v>
+        <v>18.49709512000497</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.7499684681958924</v>
+        <v>0.7808013114656017</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.0772405706011771</v>
+        <v>0.0323553241354109</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8423</v>
+        <v>8101</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>180.7634421606841</v>
+        <v>191.8491065808963</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>17.8</v>
+        <v>13.9</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>51.58302937219249</v>
+        <v>54.01575225329805</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>13.95585563570629</v>
+        <v>12.01319565585825</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.7109951457168818</v>
+        <v>0.1321942307341771</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0264759290760759</v>
+        <v>0.0802758112579878</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8249</v>
+        <v>8477</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>178.0061948258946</v>
+        <v>191.107833446731</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>44.2</v>
+        <v>15.7</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>32.80593381904933</v>
+        <v>43.66880654878231</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>16.76059935177298</v>
+        <v>11.59743450407498</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.4693241199261871</v>
+        <v>0.3549141663447051</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.2754435304321931</v>
+        <v>-0.0368426388481518</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8092</v>
+        <v>8201</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>175.9912730043403</v>
+        <v>187.9277744709509</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>13.8</v>
+        <v>12.1</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>42.64028369322399</v>
+        <v>37.47903948525873</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>14.15567041627647</v>
+        <v>13.44677456487144</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.4883083347404154</v>
+        <v>0.7499684681958924</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.08084218845733369</v>
+        <v>-0.0772405706011771</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>9955</v>
+        <v>8423</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>173.2613331029251</v>
+        <v>180.7634421606841</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>24.5</v>
+        <v>17.8</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>35.86132634932716</v>
+        <v>51.58302937219249</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>29.14906787160352</v>
+        <v>13.95585563570629</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.7463117278565461</v>
+        <v>0.7109951457168818</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.1238441859781173</v>
+        <v>0.0264759290760759</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>9910</v>
+        <v>8249</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>171.1015683452905</v>
+        <v>178.0061948258946</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>68.3</v>
+        <v>44.2</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>44.42866593302329</v>
+        <v>32.80593381904933</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>14.89136241542511</v>
+        <v>16.76059935177298</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.048511785490259</v>
+        <v>0.4693241199261871</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.2488518463500386</v>
+        <v>-0.2754435304321931</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8440</v>
+        <v>8092</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>169.4286221680202</v>
+        <v>175.9912730043403</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>20.1</v>
+        <v>13.8</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>31.71157967455962</v>
+        <v>42.64028369322399</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>15.29334833893423</v>
+        <v>14.15567041627647</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.932182532063466</v>
+        <v>0.4883083347404154</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.09753695706950991</v>
+        <v>0.08084218845733369</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8431</v>
+        <v>9955</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>168.6255588495175</v>
+        <v>173.2613331029251</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>49.15</v>
+        <v>24.5</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>45.07036775723734</v>
+        <v>35.86132634932716</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>18.20155669348221</v>
+        <v>29.14906787160352</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.05970219770929</v>
+        <v>0.7463117278565461</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.0341080726686484</v>
+        <v>-0.1238441859781173</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>8472</v>
+        <v>9910</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>161.4177907517883</v>
+        <v>171.1015683452905</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>69</v>
+        <v>68.3</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>30.58842693991623</v>
+        <v>44.42866593302329</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>14.60694484240217</v>
+        <v>14.89136241542511</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.6717988905791423</v>
+        <v>1.048511785490259</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-1.391596538120569</v>
+        <v>0.2488518463500386</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8487</v>
+        <v>8440</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>156.8226549679943</v>
+        <v>169.4286221680202</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>75.2</v>
+        <v>20.1</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>37.05950183526018</v>
+        <v>31.71157967455962</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>19.32389294387753</v>
+        <v>15.29334833893423</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.9907112279876876</v>
+        <v>0.932182532063466</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.2380907332423341</v>
+        <v>-0.09753695706950991</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5827,21 +5827,21 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8467</v>
+        <v>8431</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>152.7607098226974</v>
+        <v>168.6255588495175</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>105</v>
+        <v>49.15</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>43.81696968615397</v>
+        <v>45.07036775723734</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>13.62008678411071</v>
+        <v>18.20155669348221</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.9221385183571524</v>
+        <v>1.05970219770929</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.3547801510792379</v>
+        <v>-0.0341080726686484</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8429</v>
+        <v>8472</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>151.9376101700168</v>
+        <v>161.4177907517883</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>6.11</v>
+        <v>69</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>39.92599437798399</v>
+        <v>30.58842693991623</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>13.82620482726573</v>
+        <v>14.60694484240217</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.5565736778182414</v>
+        <v>0.6717988905791423</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.012837368428516</v>
+        <v>-1.391596538120569</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8940</v>
+        <v>8487</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>149.4460943190251</v>
+        <v>156.8226549679943</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>16.1</v>
+        <v>75.2</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>39.8831654197396</v>
+        <v>37.05950183526018</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>15.47334889158219</v>
+        <v>19.32389294387753</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.131696057593347</v>
+        <v>0.9907112279876876</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.0242886432098391</v>
+        <v>-0.2380907332423341</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8072</v>
+        <v>8467</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>149.2348110885705</v>
+        <v>152.7607098226974</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>27.4</v>
+        <v>105</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>42.24394035726414</v>
+        <v>43.81696968615397</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>16.52629153602158</v>
+        <v>13.62008678411071</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.1949036525462878</v>
+        <v>0.9221385183571524</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.2408369361507001</v>
+        <v>-0.3547801510792379</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8277</v>
+        <v>8429</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>146.7513750049552</v>
+        <v>151.9376101700168</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>8.119999999999999</v>
+        <v>6.11</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>38.84567234484212</v>
+        <v>39.92599437798399</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>23.86789711195028</v>
+        <v>13.82620482726573</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.4120012752094514</v>
+        <v>0.5565736778182414</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.123125516250547</v>
+        <v>-0.012837368428516</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>9110</v>
+        <v>8940</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>142.1548006845732</v>
+        <v>149.4460943190251</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>3.15</v>
+        <v>16.1</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>51.39692083910901</v>
+        <v>39.8831654197396</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>9.892777442158522</v>
+        <v>15.47334889158219</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.08410411248084</v>
+        <v>1.131696057593347</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.1104077669263599</v>
+        <v>-0.0242886432098391</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>8341</v>
+        <v>8072</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>135.378122663292</v>
+        <v>149.2348110885705</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>75.7</v>
+        <v>27.4</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>43.0674385900976</v>
+        <v>42.24394035726414</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>13.88951367233062</v>
+        <v>16.52629153602158</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.901185296679806</v>
+        <v>0.1949036525462878</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0562275030575486</v>
+        <v>-0.2408369361507001</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6198,21 +6198,21 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>9902</v>
+        <v>8277</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>台火</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>133.6987271550178</v>
+        <v>146.7513750049552</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>13.8</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>50.23283026376347</v>
+        <v>38.84567234484212</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>13.13955634040666</v>
+        <v>23.86789711195028</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.117571334674893</v>
+        <v>0.4120012752094514</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0066602605578978</v>
+        <v>-0.123125516250547</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8087</v>
+        <v>9110</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>132.1710875378211</v>
+        <v>142.1548006845732</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>28.1</v>
+        <v>3.15</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>34.28228863229657</v>
+        <v>51.39692083910901</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>17.27786491553311</v>
+        <v>9.892777442158522</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.239778768979091</v>
+        <v>0.08410411248084</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.3406517929616939</v>
+        <v>-0.1104077669263599</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>9906</v>
+        <v>8341</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>欣巴巴</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>81.00556172321424</v>
+        <v>135.378122663292</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>40.15</v>
+        <v>75.7</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>46.53969492547232</v>
+        <v>43.0674385900976</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>19.50379073536384</v>
+        <v>13.88951367233062</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.7657624472612259</v>
+        <v>0.901185296679806</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.2650777242884322</v>
+        <v>-0.0562275030575486</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6357,21 +6357,21 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8084</v>
+        <v>9902</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>巨虹</t>
+          <t>台火</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>78.4727155050102</v>
+        <v>133.6987271550178</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>44.5</v>
+        <v>13.8</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>39.9134508101959</v>
+        <v>50.23283026376347</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>15.88609377036585</v>
+        <v>13.13955634040666</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.163389733073169</v>
+        <v>1.117571334674893</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.4499892873188025</v>
+        <v>0.0066602605578978</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6410,21 +6410,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>8463</v>
+        <v>8087</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>74.82612285357249</v>
+        <v>132.1710875378211</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>21.3</v>
+        <v>28.1</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>44.63029780239535</v>
+        <v>34.28228863229657</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>9.740288697910692</v>
+        <v>17.27786491553311</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.5121053111662675</v>
+        <v>0.239778768979091</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0099802963370825</v>
+        <v>-0.3406517929616939</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6463,52 +6463,211 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
+        <v>9906</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>欣巴巴</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>81.00556172321424</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>46.53969492547232</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>19.50379073536384</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>0.7657624472612259</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>-0.2650777242884322</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>8084</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>巨虹</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>78.4727155050102</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>39.9134508101959</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>15.88609377036585</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>1.163389733073169</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>-0.4499892873188025</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>8463</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>潤泰材</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>74.82612285357249</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>44.63029780239535</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>9.740288697910692</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.5121053111662675</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>0.0099802963370825</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
         <v>8410</v>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>森田</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D114" s="2" t="n">
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
         <v>57.41006633368329</v>
       </c>
-      <c r="E114" s="2" t="n">
+      <c r="E117" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H114" s="2" t="n">
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
         <v>39.38339217562593</v>
       </c>
-      <c r="I114" s="2" t="n">
+      <c r="I117" s="2" t="n">
         <v>18.49280022162299</v>
       </c>
-      <c r="J114" s="2" t="n">
+      <c r="J117" s="2" t="n">
         <v>0.09319219375589</v>
       </c>
-      <c r="K114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M114" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N114" s="2" t="n">
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
         <v>-0.0299741558210728</v>
       </c>
-      <c r="O114" s="2" t="inlineStr">
+      <c r="O117" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
